--- a/ig/DM-DECEMBRE-2025/ValueSet-JDV-J129-CategorieEtablissement-RASS.xlsx
+++ b/ig/DM-DECEMBRE-2025/ValueSet-JDV-J129-CategorieEtablissement-RASS.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="649">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="651">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20241025120000</t>
+    <t>20251222120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-25T12:00:00+01:00</t>
+    <t>2025-12-22T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1921,6 +1921,12 @@
   </si>
   <si>
     <t>Structure qui contribue au Service d'Accès aux Soins</t>
+  </si>
+  <si>
+    <t>649</t>
+  </si>
+  <si>
+    <t>Centre de santé et de médiation en santé sexuelle</t>
   </si>
   <si>
     <t>695</t>
@@ -2221,7 +2227,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B312"/>
+  <dimension ref="A1:B313"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -4713,15 +4719,23 @@
         <v>646</v>
       </c>
       <c r="B311" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B312" t="s" s="2">
         <v>648</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="B313" t="s" s="2">
+        <v>650</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM-DECEMBRE-2025/ValueSet-JDV-J129-CategorieEtablissement-RASS.xlsx
+++ b/ig/DM-DECEMBRE-2025/ValueSet-JDV-J129-CategorieEtablissement-RASS.xlsx
@@ -672,7 +672,7 @@
     <t>231</t>
   </si>
   <si>
-    <t>Etablissement Information Consultation Conseil Familial</t>
+    <t>Espaces de vie affective, relationnelle et sexuelle (EVARS)</t>
   </si>
   <si>
     <t>233</t>
@@ -1764,7 +1764,7 @@
     <t>617</t>
   </si>
   <si>
-    <t>Maison médicale de garde (MMG)</t>
+    <t>Lieu de soins non programmés</t>
   </si>
   <si>
     <t>618</t>
